--- a/docs/calculator/v1.3/evidence/transfection.xlsx
+++ b/docs/calculator/v1.3/evidence/transfection.xlsx
@@ -17,13 +17,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>unit</t>
+    <t>Mix group</t>
+  </si>
+  <si>
+    <t>Tube</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Per well (µL)</t>
+  </si>
+  <si>
+    <t>Prepare batch (µL)</t>
+  </si>
+  <si>
+    <t>DNA per well (µg)</t>
   </si>
   <si>
     <t>operations</t>
@@ -68,16 +77,22 @@
     <t>structuredWarnings</t>
   </si>
   <si>
-    <t>DNA</t>
+    <t>DNA group</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Plasmid</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>13.200000000000001</t>
   </si>
   <si>
-    <t>µg</t>
-  </si>
-  <si>
-    <t>[{"id":"transfection:reagentUl","component":"转染试剂 / Transfection reagent","source":"specified-stock","destination":"preparation","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","componentId":"reagentUl","role":"add","quantity":{"value":39.6,"unit":"µL","dimension":"volume"}},{"id":"transfection:dnaVolumeUl","component":"DNA原液 / DNA solution","source":"specified-stock","destination":"preparation","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","componentId":"dnaVolumeUl","role":"add","quantity":{"value":13.200000000000001,"unit":"µL","dimension":"volume"}},{"id":"transfection:diluentUl","component":"稀释液 / Diluent","source":"specified-stock","destination":"preparation","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","componentId":"diluentUl","role":"add","quantity":{"value":772.2,"unit":"µL","dimension":"volume"}},{"id":"transfection:per-well","component":"每孔复合物 / Complex per well","source":"prepared-complex","destination":"wells","repetitions":6,"planVersion":"liquid-operations-v2","basis":"theoretical","role":"dispense","quantity":{"value":125.00000000000001,"unit":"µL","dimension":"volume"}}]</t>
+    <t>[{"id":"transfection:0:0","component":"Plasmid","source":"Plasmid","destination":"DNA group:A","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"add","quantity":{"value":13.200000000000001,"unit":"µL","dimension":"volume"}},{"id":"transfection:0:1","component":"Opti-MEM","source":"Opti-MEM","destination":"DNA group:A","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"add","quantity":{"value":399.3,"unit":"µL","dimension":"volume"}},{"id":"transfection:0:2","component":"Custom lipid","source":"Custom lipid","destination":"DNA group:B","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"add","quantity":{"value":39.6,"unit":"µL","dimension":"volume"}},{"id":"transfection:0:3","component":"Opti-MEM","source":"Opti-MEM","destination":"DNA group:B","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"add","quantity":{"value":372.90000000000003,"unit":"µL","dimension":"volume"}},{"id":"transfection:0:combine","component":"合并A至B / Combine A into B","source":"DNA group:A","destination":"DNA group:B","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"transfer","quantity":{"value":412.50000000000006,"unit":"µL","dimension":"volume"}},{"id":"transfection:0:dispense","component":"每孔混合液 / Mixture per well","source":"DNA group:mixture","destination":"DNA group:wells","repetitions":6,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"dispense","quantity":{"value":125.00000000000001,"unit":"µL","dimension":"volume"}}]</t>
   </si>
   <si>
     <t>liquid-operations-v2</t>
@@ -95,67 +110,98 @@
     <t>default</t>
   </si>
   <si>
-    <t>transfection-v2</t>
+    <t>transfection-v3</t>
   </si>
   <si>
     <t>valid</t>
   </si>
   <si>
-    <t>试剂、稀释液及混合顺序遵循所用产品说明 / Follow product-specific reagent, diluent and mixing instructions</t>
-  </si>
-  <si>
-    <t>{"complexMode":"combined","wells":6,"replicates":1,"dnaUgPerWell":2,"dnaConcentrationUgUl":1,"reagentUlPerUg":3,"complexVolumeUlPerWell":125,"overagePercent":10,"tubeAVolumeUl":""}</t>
-  </si>
-  <si>
-    <t>[{"key":"dnaUg","label":"DNA","labelZh":"DNA","value":13.200000000000001,"unit":"µg"},{"key":"reagentUl","label":"Transfection reagent","labelZh":"转染试剂","value":39.6,"unit":"µL"},{"key":"dnaVolumeUl","label":"DNA solution","labelZh":"DNA原液","value":13.200000000000001,"unit":"µL"},{"key":"diluentUl","label":"Diluent","labelZh":"稀释液","value":772.2,"unit":"µL"},{"key":"totalComplexUl","label":"Total complex","labelZh":"复合物总量","value":825.0000000000001,"unit":"µL"}]</t>
+    <t>方案用量需按所用试剂与细胞条件验证；不同实验组分别配制。 / Validate doses for reagent and cells; prepare each experimental group separately.</t>
+  </si>
+  <si>
+    <t>DNA group: A管核酸稀释后与B管稀释试剂混合，按已验证方案孵育，再加入细胞。 / Dilute nucleic acid in A and reagent in B; combine and follow the validated protocol before adding to cells.
+体积按可加和计算；siRNA nM × 最终培养体积µL ÷1000 = pmol；µM = pmol/µL。余量仅放大备料，不增加每孔剂量。 / Additive volumes; overage increases supplies only.</t>
+  </si>
+  <si>
+    <t>{"complexMode":"combined","wells":"","replicates":"","dnaUgPerWell":"","dnaConcentrationUgUl":"","reagentUlPerUg":"","complexVolumeUlPerWell":"","overagePercent":"","tubeAVolumeUl":"","transfectionPlan":{"version":3,"material":"dna","mixing":"two-tube","protocol":"custom","groups":[{"name":"DNA group","wells":"6","overage":"10","finalVolume":"1000","dnaMode":"amount","totalDna":"","rnaMode":"each-nm","totalRna":"","rows":[{"name":"Plasmid","kind":"dna","stock":"1","stockUnit":"µg/µL","dose":"2","sizeBasis":"bp","size":""}],"reagent":{"name":"Custom lipid","basis":"dna","amount":"3","basisName":"","basisUnit":"","basisAmount":""},"auxiliaries":[],"a":{"mode":"final","value":"62.5"},"b":{"mode":"final","value":"62.5"},"single":{"mode":"final","value":""},"diluent":"Opti-MEM","order":"A管核酸稀释后与B管稀释试剂混合，按已验证方案孵育，再加入细胞。 / Dilute nucleic acid in A and reagent in B; combine and follow the validated protocol before adding to cells."}]}}</t>
+  </si>
+  <si>
+    <t>[{"key":"group0_dna","label":"DNA group · DNA per well","labelZh":"DNA group · 每孔总DNA","value":2,"unit":"µg"},{"key":"group0_a","label":"DNA group · Tube A total per well","labelZh":"DNA group · 每孔A管总体积","value":62.5,"unit":"µL"},{"key":"group0_b","label":"DNA group · Tube B total per well","labelZh":"DNA group · 每孔B管总体积","value":62.5,"unit":"µL"},{"key":"group0_mixed","label":"DNA group · Mixture added per well","labelZh":"DNA group · 每孔混合液加入量","value":125,"unit":"µL"},{"key":"group0_final","label":"DNA group · Final culture volume per well","labelZh":"DNA group · 每孔最终培养体积","value":1000,"unit":"µL"},{"key":"group0_medium","label":"DNA group · Cell medium before addition","labelZh":"DNA group · 加入混合液前培养基/细胞悬液","value":875,"unit":"µL"},{"key":"group0_batch","label":"DNA group · Batch supply incl. overage","labelZh":"DNA group · 含余量整批备料体积","value":825.0000000000001,"unit":"µL"},{"key":"dnaUg","label":"Batch DNA incl. overage","labelZh":"含余量整批DNA","value":13.200000000000001,"unit":"µg"}]</t>
   </si>
   <si>
     <t>[]</t>
   </si>
   <si>
-    <t>Transfection reagent</t>
+    <t>Opti-MEM</t>
+  </si>
+  <si>
+    <t>60.5</t>
+  </si>
+  <si>
+    <t>399.3</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Custom lipid</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>39.6</t>
   </si>
   <si>
-    <t>µL</t>
-  </si>
-  <si>
-    <t>DNA solution</t>
-  </si>
-  <si>
-    <t>Diluent</t>
-  </si>
-  <si>
-    <t>772.2</t>
-  </si>
-  <si>
-    <t>Total complex</t>
-  </si>
-  <si>
-    <t>825.0000000000001</t>
+    <t>56.5</t>
+  </si>
+  <si>
+    <t>372.90000000000003</t>
   </si>
   <si>
     <t>transfection · default</t>
   </si>
   <si>
-    <t>DNA: 13.2 µg</t>
-  </si>
-  <si>
-    <t>Transfection reagent: 39.6 µL</t>
-  </si>
-  <si>
-    <t>DNA solution: 13.2 µL</t>
-  </si>
-  <si>
-    <t>Diluent: 772.2 µL</t>
-  </si>
-  <si>
-    <t>Total complex: 825 µL</t>
-  </si>
-  <si>
-    <t>Operations (liquid-operations-v2): [{"id":"transfection:reagentUl","component":"转染试剂 / Transfection reagent","source":"specified-stock","destination":"preparation","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","componentId":"reagentUl","role":"add","quantity":{"value":39.6,"unit":"µL","dimension":"volume"}},{"id":"transfection:dnaVolumeUl","component":"DNA原液 / DNA solution","source":"specified-stock","destination":"preparation","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","componentId":"dnaVolumeUl","role":"add","quantity":{"value":13.200000000000001,"unit":"µL","dimension":"volume"}},{"id":"transfection:diluentUl","component":"稀释液 / Diluent","source":"specified-stock","destination":"preparation","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","componentId":"diluentUl","role":"add","quantity":{"value":772.2,"unit":"µL","dimension":"volume"}},{"id":"transfection:per-well","component":"每孔复合物 / Complex per well","source":"prepared-complex","destination":"wells","repetitions":6,"planVersion":"liquid-operations-v2","basis":"theoretical","role":"dispense","quantity":{"value":125.00000000000001,"unit":"µL","dimension":"volume"}}]</t>
+    <t>DNA group · DNA per well: 2 µg</t>
+  </si>
+  <si>
+    <t>DNA group · Tube A total per well: 62.5 µL</t>
+  </si>
+  <si>
+    <t>DNA group · Tube B total per well: 62.5 µL</t>
+  </si>
+  <si>
+    <t>DNA group · Mixture added per well: 125 µL</t>
+  </si>
+  <si>
+    <t>DNA group · Final culture volume per well: 1000 µL</t>
+  </si>
+  <si>
+    <t>DNA group · Cell medium before addition: 875 µL</t>
+  </si>
+  <si>
+    <t>DNA group · Batch supply incl. overage: 825 µL</t>
+  </si>
+  <si>
+    <t>Batch DNA incl. overage: 13.2 µg</t>
+  </si>
+  <si>
+    <t>Mix group	Tube	Component	Per well (µL)	Prepare batch (µL)	DNA per well (µg)</t>
+  </si>
+  <si>
+    <t>DNA group	A	Plasmid	2	13.2	2</t>
+  </si>
+  <si>
+    <t>DNA group	A	Opti-MEM	60.5	399.3</t>
+  </si>
+  <si>
+    <t>DNA group	B	Custom lipid	6	39.6</t>
+  </si>
+  <si>
+    <t>DNA group	B	Opti-MEM	56.5	372.9</t>
+  </si>
+  <si>
+    <t>Operations (liquid-operations-v2): [{"id":"transfection:0:0","component":"Plasmid","source":"Plasmid","destination":"DNA group:A","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"add","quantity":{"value":13.200000000000001,"unit":"µL","dimension":"volume"}},{"id":"transfection:0:1","component":"Opti-MEM","source":"Opti-MEM","destination":"DNA group:A","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"add","quantity":{"value":399.3,"unit":"µL","dimension":"volume"}},{"id":"transfection:0:2","component":"Custom lipid","source":"Custom lipid","destination":"DNA group:B","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"add","quantity":{"value":39.6,"unit":"µL","dimension":"volume"}},{"id":"transfection:0:3","component":"Opti-MEM","source":"Opti-MEM","destination":"DNA group:B","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"add","quantity":{"value":372.90000000000003,"unit":"µL","dimension":"volume"}},{"id":"transfection:0:combine","component":"合并A至B / Combine A into B","source":"DNA group:A","destination":"DNA group:B","repetitions":1,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"transfer","quantity":{"value":412.50000000000006,"unit":"µL","dimension":"volume"}},{"id":"transfection:0:dispense","component":"每孔混合液 / Mixture per well","source":"DNA group:mixture","destination":"DNA group:wells","repetitions":6,"planVersion":"liquid-operations-v2","basis":"theoretical","group":"0","groupName":"DNA group","role":"dispense","quantity":{"value":125.00000000000001,"unit":"µL","dimension":"volume"}}]</t>
   </si>
   <si>
     <t>Pipetting check: {"status":"not-set"}</t>
@@ -167,10 +213,16 @@
     <t>Assumptions</t>
   </si>
   <si>
-    <t>Status: valid; Method: transfection-v2</t>
-  </si>
-  <si>
-    <t>Inputs: {"complexMode":"combined","wells":6,"replicates":1,"dnaUgPerWell":2,"dnaConcentrationUgUl":1,"reagentUlPerUg":3,"complexVolumeUlPerWell":125,"overagePercent":10,"tubeAVolumeUl":""}</t>
+    <t>DNA group: A管核酸稀释后与B管稀释试剂混合，按已验证方案孵育，再加入细胞。 / Dilute nucleic acid in A and reagent in B; combine and follow the validated protocol before adding to cells.</t>
+  </si>
+  <si>
+    <t>体积按可加和计算；siRNA nM × 最终培养体积µL ÷1000 = pmol；µM = pmol/µL。余量仅放大备料，不增加每孔剂量。 / Additive volumes; overage increases supplies only.</t>
+  </si>
+  <si>
+    <t>Status: valid; Method: transfection-v3</t>
+  </si>
+  <si>
+    <t>Inputs: {"complexMode":"combined","wells":"","replicates":"","dnaUgPerWell":"","dnaConcentrationUgUl":"","reagentUlPerUg":"","complexVolumeUlPerWell":"","overagePercent":"","tubeAVolumeUl":"","transfectionPlan":{"version":3,"material":"dna","mixing":"two-tube","protocol":"custom","groups":[{"name":"DNA group","wells":"6","overage":"10","finalVolume":"1000","dnaMode":"amount","totalDna":"","rnaMode":"each-nm","totalRna":"","rows":[{"name":"Plasmid","kind":"dna","stock":"1","stockUnit":"µg/µL","dose":"2","sizeBasis":"bp","size":""}],"reagent":{"name":"Custom lipid","basis":"dna","amount":"3","basisName":"","basisUnit":"","basisAmount":""},"auxiliaries":[],"a":{"mode":"final","value":"62.5"},"b":{"mode":"final","value":"62.5"},"single":{"mode":"final","value":""},"diluent":"Opti-MEM","order":"A管核酸稀释后与B管稀释试剂混合，按已验证方案孵育，再加入细胞。 / Dilute nucleic acid in A and reagent in B; combine and follow the validated protocol before adding to cells."}]}}</t>
   </si>
   <si>
     <t>Context: {}</t>
@@ -265,255 +317,253 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
       </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+      <c r="R2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" t="s">
+      <c r="O3" t="s">
         <v>33</v>
       </c>
-      <c r="C3" t="s">
+      <c r="P3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" t="s">
-        <v>23</v>
-      </c>
       <c r="Q3" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+      <c r="R3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" t="s">
+        <v>28</v>
+      </c>
+      <c r="T3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>31</v>
+      <c r="R4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>35</v>
+      </c>
+      <c r="R5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="S5" t="s">
+        <v>28</v>
+      </c>
+      <c r="T5" t="s">
         <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -525,72 +575,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
